--- a/tests/fixtures/wbs-merged.xlsx
+++ b/tests/fixtures/wbs-merged.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="WBS（結合）" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="WBS（インデント）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="WBS（非表示）" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -650,4 +651,87 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col hidden="1" width="13" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>隠れた列</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>表示される行</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>隠れた列</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>隠れた行</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>隠れた列</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>隠れた行の期限</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>別の行</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>隠れた列</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>表示される列</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>